--- a/resource/map4.xlsx
+++ b/resource/map4.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4224" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4224" uniqueCount="148">
   <si>
     <t>0
 1345</t>
@@ -448,9 +448,6 @@
     <t>9
 1232
 5深位</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  上下货</t>
   </si>
   <si>
     <t>10
@@ -3859,7 +3856,7 @@
         <v>90</v>
       </c>
       <c r="J11" s="4" t="s">
-        <v>105</v>
+        <v>90</v>
       </c>
       <c r="K11" s="4" t="s">
         <v>90</v>
@@ -4098,7 +4095,7 @@
     </row>
     <row r="12" customHeight="1" spans="1:88">
       <c r="A12" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E12" s="4" t="s">
         <v>90</v>
@@ -4355,7 +4352,7 @@
     </row>
     <row r="13" customHeight="1" spans="1:88">
       <c r="A13" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E13" s="4" t="s">
         <v>90</v>
@@ -4613,7 +4610,7 @@
     </row>
     <row r="14" customHeight="1" spans="1:88">
       <c r="A14" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B14" s="4" t="s">
         <v>88</v>
@@ -4879,7 +4876,7 @@
     </row>
     <row r="15" customHeight="1" spans="1:88">
       <c r="A15" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B15" s="4" t="s">
         <v>90</v>
@@ -5145,7 +5142,7 @@
     </row>
     <row r="16" customHeight="1" spans="1:88">
       <c r="A16" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B16" s="6" t="s">
         <v>98</v>
@@ -5411,7 +5408,7 @@
     </row>
     <row r="17" customHeight="1" spans="1:88">
       <c r="A17" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B17" s="4" t="s">
         <v>90</v>
@@ -5426,10 +5423,10 @@
         <v>90</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H17" s="7" t="s">
         <v>103</v>
@@ -5444,7 +5441,7 @@
         <v>90</v>
       </c>
       <c r="L17" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="M17" s="4" t="s">
         <v>90</v>
@@ -5459,7 +5456,7 @@
         <v>90</v>
       </c>
       <c r="Q17" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="R17" s="4" t="s">
         <v>90</v>
@@ -5477,22 +5474,22 @@
         <v>90</v>
       </c>
       <c r="W17" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="X17" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="Y17" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="Z17" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="AA17" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="AB17" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="AC17" s="4" t="s">
         <v>90</v>
@@ -5510,7 +5507,7 @@
         <v>90</v>
       </c>
       <c r="AH17" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="AI17" s="4" t="s">
         <v>90</v>
@@ -5525,10 +5522,10 @@
         <v>90</v>
       </c>
       <c r="AM17" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="AN17" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="AO17" s="4" t="s">
         <v>90</v>
@@ -5543,7 +5540,7 @@
         <v>90</v>
       </c>
       <c r="AS17" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="AT17" s="4" t="s">
         <v>90</v>
@@ -5558,10 +5555,10 @@
         <v>90</v>
       </c>
       <c r="AX17" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="AY17" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="AZ17" s="4" t="s">
         <v>90</v>
@@ -5576,25 +5573,25 @@
         <v>90</v>
       </c>
       <c r="BD17" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="BE17" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="BF17" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="BG17" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="BH17" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="BI17" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="BJ17" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="BK17" s="4" t="s">
         <v>90</v>
@@ -5609,7 +5606,7 @@
         <v>90</v>
       </c>
       <c r="BO17" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="BP17" s="4" t="s">
         <v>90</v>
@@ -5627,7 +5624,7 @@
         <v>90</v>
       </c>
       <c r="BU17" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="BV17" s="4" t="s">
         <v>90</v>
@@ -5642,7 +5639,7 @@
         <v>103</v>
       </c>
       <c r="BZ17" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="CA17" s="4" t="s">
         <v>90</v>
@@ -5660,42 +5657,42 @@
         <v>90</v>
       </c>
       <c r="CF17" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="CG17" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="CH17" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="CI17" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="CJ17" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="18" customHeight="1" spans="1:88">
       <c r="A18" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="F18" s="8" t="s">
         <v>113</v>
       </c>
-      <c r="B18" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="D18" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="E18" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="F18" s="8" t="s">
-        <v>114</v>
-      </c>
       <c r="G18" s="8" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H18" s="7" t="s">
         <v>103</v>
@@ -5710,7 +5707,7 @@
         <v>90</v>
       </c>
       <c r="L18" s="8" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="M18" s="4" t="s">
         <v>90</v>
@@ -5725,7 +5722,7 @@
         <v>90</v>
       </c>
       <c r="Q18" s="8" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="R18" s="4" t="s">
         <v>90</v>
@@ -5743,22 +5740,22 @@
         <v>90</v>
       </c>
       <c r="W18" s="8" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="X18" s="8" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="Y18" s="8" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="Z18" s="8" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="AA18" s="8" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="AB18" s="8" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="AC18" s="4" t="s">
         <v>90</v>
@@ -5776,7 +5773,7 @@
         <v>90</v>
       </c>
       <c r="AH18" s="8" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="AI18" s="4" t="s">
         <v>90</v>
@@ -5791,10 +5788,10 @@
         <v>90</v>
       </c>
       <c r="AM18" s="8" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="AN18" s="8" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="AO18" s="4" t="s">
         <v>90</v>
@@ -5809,7 +5806,7 @@
         <v>90</v>
       </c>
       <c r="AS18" s="8" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="AT18" s="4" t="s">
         <v>90</v>
@@ -5824,10 +5821,10 @@
         <v>90</v>
       </c>
       <c r="AX18" s="8" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="AY18" s="8" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="AZ18" s="4" t="s">
         <v>90</v>
@@ -5842,25 +5839,25 @@
         <v>90</v>
       </c>
       <c r="BD18" s="8" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="BE18" s="8" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="BF18" s="8" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="BG18" s="8" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="BH18" s="8" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="BI18" s="8" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="BJ18" s="8" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="BK18" s="4" t="s">
         <v>90</v>
@@ -5875,7 +5872,7 @@
         <v>90</v>
       </c>
       <c r="BO18" s="8" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="BP18" s="4" t="s">
         <v>90</v>
@@ -5893,7 +5890,7 @@
         <v>90</v>
       </c>
       <c r="BU18" s="8" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="BV18" s="4" t="s">
         <v>90</v>
@@ -5908,7 +5905,7 @@
         <v>103</v>
       </c>
       <c r="BZ18" s="8" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="CA18" s="4" t="s">
         <v>90</v>
@@ -5926,24 +5923,24 @@
         <v>90</v>
       </c>
       <c r="CF18" s="8" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="CG18" s="8" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="CH18" s="8" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="CI18" s="8" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="CJ18" s="8" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="19" customHeight="1" spans="1:88">
       <c r="A19" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>90</v>
@@ -6209,7 +6206,7 @@
     </row>
     <row r="20" customHeight="1" spans="1:88">
       <c r="A20" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B20" s="4" t="s">
         <v>90</v>
@@ -6475,7 +6472,7 @@
     </row>
     <row r="21" customHeight="1" spans="1:88">
       <c r="A21" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B21" s="4" t="s">
         <v>90</v>
@@ -6741,16 +6738,16 @@
     </row>
     <row r="22" customHeight="1" spans="1:88">
       <c r="A22" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E22" s="4" t="s">
         <v>90</v>
@@ -7007,7 +7004,7 @@
     </row>
     <row r="23" customHeight="1" spans="1:88">
       <c r="A23" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E23" s="4" t="s">
         <v>90</v>
@@ -7264,7 +7261,7 @@
     </row>
     <row r="24" customHeight="1" spans="1:88">
       <c r="A24" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E24" s="4" t="s">
         <v>90</v>
@@ -7521,7 +7518,7 @@
     </row>
     <row r="25" customHeight="1" spans="1:88">
       <c r="A25" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E25" s="4" t="s">
         <v>90</v>
@@ -7778,7 +7775,7 @@
     </row>
     <row r="26" customHeight="1" spans="1:88">
       <c r="A26" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D26" s="4" t="s">
         <v>88</v>
@@ -8038,7 +8035,7 @@
     </row>
     <row r="27" customHeight="1" spans="1:88">
       <c r="A27" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D27" s="6" t="s">
         <v>99</v>
@@ -8298,13 +8295,13 @@
     </row>
     <row r="28" customHeight="1" spans="1:88">
       <c r="A28" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D28" s="5" t="s">
         <v>102</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F28" s="4" t="s">
         <v>90</v>
@@ -8558,7 +8555,7 @@
     </row>
     <row r="29" customHeight="1" spans="1:88">
       <c r="A29" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F29" s="4" t="s">
         <v>90</v>
@@ -8812,7 +8809,7 @@
     </row>
     <row r="30" customHeight="1" spans="1:88">
       <c r="A30" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F30" s="4" t="s">
         <v>90</v>
@@ -9066,7 +9063,7 @@
     </row>
     <row r="31" customHeight="1" spans="1:88">
       <c r="A31" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E31" s="4" t="s">
         <v>88</v>
@@ -9323,7 +9320,7 @@
     </row>
     <row r="32" customHeight="1" spans="1:88">
       <c r="A32" s="3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E32" s="4" t="s">
         <v>90</v>
@@ -9580,7 +9577,7 @@
     </row>
     <row r="33" customHeight="1" spans="1:88">
       <c r="A33" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E33" s="4" t="s">
         <v>90</v>
@@ -9837,7 +9834,7 @@
     </row>
     <row r="34" customHeight="1" spans="1:88">
       <c r="A34" s="3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E34" s="4" t="s">
         <v>90</v>
@@ -10094,7 +10091,7 @@
     </row>
     <row r="35" customHeight="1" spans="1:88">
       <c r="A35" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D35" s="4" t="s">
         <v>88</v>
@@ -10103,10 +10100,10 @@
         <v>90</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G35" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H35" s="7" t="s">
         <v>103</v>
@@ -10121,7 +10118,7 @@
         <v>90</v>
       </c>
       <c r="L35" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="M35" s="4" t="s">
         <v>90</v>
@@ -10136,7 +10133,7 @@
         <v>90</v>
       </c>
       <c r="Q35" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="R35" s="4" t="s">
         <v>90</v>
@@ -10154,22 +10151,22 @@
         <v>90</v>
       </c>
       <c r="W35" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="X35" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="Y35" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="Z35" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="AA35" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="AB35" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="AC35" s="4" t="s">
         <v>90</v>
@@ -10187,10 +10184,10 @@
         <v>90</v>
       </c>
       <c r="AH35" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="AI35" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="AJ35" s="4" t="s">
         <v>90</v>
@@ -10202,10 +10199,10 @@
         <v>90</v>
       </c>
       <c r="AM35" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="AN35" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="AO35" s="4" t="s">
         <v>90</v>
@@ -10220,7 +10217,7 @@
         <v>90</v>
       </c>
       <c r="AS35" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="AT35" s="4" t="s">
         <v>90</v>
@@ -10235,10 +10232,10 @@
         <v>90</v>
       </c>
       <c r="AX35" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="AY35" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="AZ35" s="4" t="s">
         <v>90</v>
@@ -10250,28 +10247,28 @@
         <v>90</v>
       </c>
       <c r="BC35" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="BD35" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="BE35" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="BF35" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="BG35" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="BH35" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="BI35" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="BJ35" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="BK35" s="4" t="s">
         <v>90</v>
@@ -10286,7 +10283,7 @@
         <v>90</v>
       </c>
       <c r="BO35" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="BP35" s="4" t="s">
         <v>90</v>
@@ -10304,7 +10301,7 @@
         <v>90</v>
       </c>
       <c r="BU35" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="BV35" s="4" t="s">
         <v>90</v>
@@ -10319,10 +10316,10 @@
         <v>103</v>
       </c>
       <c r="BZ35" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="CA35" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="CB35" s="4" t="s">
         <v>90</v>
@@ -10337,24 +10334,24 @@
         <v>90</v>
       </c>
       <c r="CF35" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="CG35" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="CH35" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="CI35" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="CJ35" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="36" customHeight="1" spans="1:88">
       <c r="A36" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D36" s="4" t="s">
         <v>90</v>
@@ -10363,10 +10360,10 @@
         <v>90</v>
       </c>
       <c r="F36" s="8" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G36" s="8" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H36" s="7" t="s">
         <v>103</v>
@@ -10381,7 +10378,7 @@
         <v>90</v>
       </c>
       <c r="L36" s="8" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="M36" s="4" t="s">
         <v>90</v>
@@ -10396,7 +10393,7 @@
         <v>90</v>
       </c>
       <c r="Q36" s="8" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="R36" s="4" t="s">
         <v>90</v>
@@ -10414,22 +10411,22 @@
         <v>90</v>
       </c>
       <c r="W36" s="8" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="X36" s="8" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="Y36" s="8" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="Z36" s="8" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="AA36" s="8" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="AB36" s="8" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="AC36" s="4" t="s">
         <v>90</v>
@@ -10447,10 +10444,10 @@
         <v>90</v>
       </c>
       <c r="AH36" s="8" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="AI36" s="8" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="AJ36" s="4" t="s">
         <v>90</v>
@@ -10462,10 +10459,10 @@
         <v>90</v>
       </c>
       <c r="AM36" s="8" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="AN36" s="8" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="AO36" s="4" t="s">
         <v>90</v>
@@ -10480,7 +10477,7 @@
         <v>90</v>
       </c>
       <c r="AS36" s="8" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="AT36" s="4" t="s">
         <v>90</v>
@@ -10495,10 +10492,10 @@
         <v>90</v>
       </c>
       <c r="AX36" s="8" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="AY36" s="8" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="AZ36" s="4" t="s">
         <v>90</v>
@@ -10510,28 +10507,28 @@
         <v>90</v>
       </c>
       <c r="BC36" s="8" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="BD36" s="8" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="BE36" s="8" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="BF36" s="8" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="BG36" s="8" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="BH36" s="8" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="BI36" s="8" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="BJ36" s="8" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="BK36" s="4" t="s">
         <v>90</v>
@@ -10546,7 +10543,7 @@
         <v>90</v>
       </c>
       <c r="BO36" s="8" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="BP36" s="4" t="s">
         <v>90</v>
@@ -10564,7 +10561,7 @@
         <v>90</v>
       </c>
       <c r="BU36" s="8" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="BV36" s="4" t="s">
         <v>90</v>
@@ -10579,10 +10576,10 @@
         <v>103</v>
       </c>
       <c r="BZ36" s="8" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="CA36" s="8" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="CB36" s="4" t="s">
         <v>90</v>
@@ -10597,24 +10594,24 @@
         <v>90</v>
       </c>
       <c r="CF36" s="8" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="CG36" s="8" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="CH36" s="8" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="CI36" s="8" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="CJ36" s="8" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="37" customHeight="1" spans="1:88">
       <c r="A37" s="3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D37" s="4" t="s">
         <v>90</v>
@@ -10623,10 +10620,10 @@
         <v>90</v>
       </c>
       <c r="F37" s="8" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G37" s="8" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H37" s="7" t="s">
         <v>103</v>
@@ -10707,10 +10704,10 @@
         <v>90</v>
       </c>
       <c r="AH37" s="8" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="AI37" s="8" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="AJ37" s="4" t="s">
         <v>90</v>
@@ -10839,10 +10836,10 @@
         <v>103</v>
       </c>
       <c r="BZ37" s="8" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="CA37" s="8" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="CB37" s="4" t="s">
         <v>90</v>
@@ -10874,7 +10871,7 @@
     </row>
     <row r="38" customHeight="1" spans="1:88">
       <c r="A38" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D38" s="4" t="s">
         <v>90</v>
@@ -11134,7 +11131,7 @@
     </row>
     <row r="39" customHeight="1" spans="1:88">
       <c r="A39" s="3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D39" s="6" t="s">
         <v>99</v>
@@ -11394,7 +11391,7 @@
     </row>
     <row r="40" customHeight="1" spans="1:88">
       <c r="A40" s="3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D40" s="4" t="s">
         <v>90</v>
@@ -11654,7 +11651,7 @@
     </row>
     <row r="41" customHeight="1" spans="1:88">
       <c r="A41" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D41" s="4" t="s">
         <v>90</v>
@@ -11914,7 +11911,7 @@
     </row>
     <row r="42" customHeight="1" spans="1:88">
       <c r="A42" s="3" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D42" s="4" t="s">
         <v>90</v>
@@ -12174,7 +12171,7 @@
     </row>
     <row r="43" customHeight="1" spans="1:88">
       <c r="A43" s="3" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D43" s="4" t="s">
         <v>90</v>
@@ -12434,7 +12431,7 @@
     </row>
     <row r="44" customHeight="1" spans="1:88">
       <c r="A44" s="3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D44" s="4" t="s">
         <v>90</v>
@@ -12694,7 +12691,7 @@
     </row>
     <row r="45" customHeight="1" spans="1:88">
       <c r="A45" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D45" s="4" t="s">
         <v>90</v>
@@ -12954,7 +12951,7 @@
     </row>
     <row r="46" customHeight="1" spans="1:88">
       <c r="A46" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D46" s="4" t="s">
         <v>90</v>
@@ -13214,7 +13211,7 @@
     </row>
     <row r="47" customHeight="1" spans="1:88">
       <c r="A47" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D47" s="6" t="s">
         <v>99</v>
@@ -13474,7 +13471,7 @@
     </row>
     <row r="48" customHeight="1" spans="1:88">
       <c r="A48" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D48" s="4" t="s">
         <v>90</v>
@@ -13507,13 +13504,13 @@
         <v>102</v>
       </c>
       <c r="N48" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="O48" s="5" t="s">
         <v>102</v>
       </c>
       <c r="P48" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="Q48" s="4" t="s">
         <v>90</v>
@@ -13591,13 +13588,13 @@
         <v>102</v>
       </c>
       <c r="AP48" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="AQ48" s="5" t="s">
         <v>102</v>
       </c>
       <c r="AR48" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="AS48" s="4" t="s">
         <v>90</v>
@@ -13734,7 +13731,7 @@
     </row>
     <row r="49" customHeight="1" spans="1:88">
       <c r="A49" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D49" s="4" t="s">
         <v>90</v>
@@ -13970,7 +13967,7 @@
     </row>
     <row r="50" customHeight="1" spans="1:88">
       <c r="A50" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D50" s="4" t="s">
         <v>90</v>
@@ -13997,7 +13994,7 @@
         <v>90</v>
       </c>
       <c r="L50" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="Q50" s="4" t="s">
         <v>90</v>
@@ -14069,7 +14066,7 @@
         <v>90</v>
       </c>
       <c r="AN50" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="AS50" s="4" t="s">
         <v>90</v>
@@ -14206,7 +14203,7 @@
     </row>
     <row r="51" customHeight="1" spans="1:88">
       <c r="A51" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D51" s="4" t="s">
         <v>90</v>
@@ -14436,232 +14433,232 @@
     </row>
     <row r="52" customHeight="1" spans="1:88">
       <c r="A52" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G52" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H52" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="I52" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="J52" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="K52" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="Q52" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="R52" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="S52" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="T52" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="U52" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="V52" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="W52" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="X52" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="Y52" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="Z52" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="AA52" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="AB52" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="AC52" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="AD52" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="AE52" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="AF52" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="AG52" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="AH52" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="AI52" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="AJ52" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="AK52" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="AL52" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="AM52" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="AS52" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="AT52" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="AU52" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="AV52" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="AW52" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="AX52" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="AY52" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="AZ52" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="BA52" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="BB52" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="BC52" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="BD52" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="BE52" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="BF52" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="BG52" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="BH52" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="BI52" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="BJ52" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="BK52" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="BL52" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="BM52" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="BN52" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="BO52" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="BP52" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="BQ52" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="BR52" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="BS52" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="BT52" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="BU52" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="BV52" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="BW52" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="BX52" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="BY52" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="BZ52" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="CA52" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="CB52" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="CC52" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="CD52" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="CE52" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="CF52" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="CG52" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="CH52" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="CI52" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="CJ52" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
   </sheetData>
